--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
@@ -72,12 +72,12 @@
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:02</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4303</v>
+        <v>4105</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>614580.25</v>
+        <v>652930.94</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4303</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>614580.25</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:45</t>
+    <t xml:space="preserve">2026-10-04 08:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:49</t>
+    <t xml:space="preserve">2026-10-05 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -557,7 +557,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>875008.62</v>
+        <v>875008.63</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>861049.62</v>
+        <v>861049.63</v>
       </c>
     </row>
     <row r="6">
@@ -659,7 +659,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>734508.12</v>
+        <v>734508.13</v>
       </c>
     </row>
     <row r="11">
@@ -693,7 +693,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>715971.62</v>
+        <v>715971.63</v>
       </c>
     </row>
     <row r="13">
